--- a/database/DATA_DICTIONARY.xlsx
+++ b/database/DATA_DICTIONARY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natthapornkit\Downloads\Project\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECDFD54-A0BB-4E67-A3D8-51F9A4E0AD94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C258310A-B505-40CE-B957-F2710560B429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4275" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -634,14 +634,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1033,7 +1033,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="9"/>
@@ -1059,7 +1059,7 @@
       <c r="B19" s="9"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="9"/>
@@ -1085,7 +1085,7 @@
       <c r="B25" s="9"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="9"/>
@@ -1111,7 +1111,7 @@
       <c r="B31" s="9"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B32" s="9"/>
@@ -1137,7 +1137,7 @@
       <c r="B37" s="9"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B38" s="9"/>
@@ -1163,7 +1163,7 @@
       <c r="B43" s="9"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="9"/>
@@ -1218,7 +1218,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="9"/>
@@ -1366,7 +1366,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>164</v>
       </c>
       <c r="B14" s="9"/>
@@ -1550,7 +1550,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="9"/>
@@ -1747,7 +1747,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>85</v>
       </c>
       <c r="B17" s="9"/>
@@ -1781,7 +1781,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="9"/>
@@ -1880,7 +1880,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>92</v>
       </c>
       <c r="B11" s="9"/>
@@ -1904,7 +1904,7 @@
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1914,7 +1914,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="9"/>
@@ -2266,7 +2266,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B26" s="9"/>
@@ -2300,7 +2300,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="9"/>
@@ -2382,7 +2382,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B10" s="9"/>
@@ -2416,7 +2416,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="9"/>
@@ -2583,7 +2583,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>152</v>
       </c>
       <c r="B15" s="9"/>
@@ -2617,7 +2617,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="9"/>
@@ -2778,7 +2778,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>152</v>
       </c>
       <c r="B15" s="9"/>
